--- a/reports/Kommune_Project_Controller_Reporting_2026.xlsx
+++ b/reports/Kommune_Project_Controller_Reporting_2026.xlsx
@@ -625,12 +625,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="146" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
@@ -797,22 +797,22 @@
     <row r="12">
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Kommunal Boenhet</t>
+          <t>Barnehageavdelingen (54 barnehager)</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Helse og mestring</t>
+          <t>Oppvekst og utdanning</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>50339572</v>
+        <v>720000000.01</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>39650784</v>
+        <v>720000000.01</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>47426243.51</v>
+        <v>731000000</v>
       </c>
       <c r="G12" s="12">
         <f>E12-F12</f>
@@ -838,22 +838,22 @@
     <row r="13">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Digitaliseringsavdelingen</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Oppvekst og utdanning</t>
+          <t>Organisasjon og teknologi</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>33591000</v>
+        <v>60000000.01</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>31983000</v>
+        <v>60000000.01</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>36080000</v>
+        <v>60000000.01</v>
       </c>
       <c r="G13" s="12">
         <f>E13-F13</f>
@@ -877,75 +877,1756 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Døgnomsorg og Sykehjem</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>959999999.99</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>959999999.99</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>978249999.99</v>
+      </c>
+      <c r="G14" s="12">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="13">
+        <f>IF(F14&gt;0, E14/F14, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="14">
+        <f>IF(H14&gt;0, D14/H14, D14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="12">
+        <f>I14-D14</f>
+        <v/>
+      </c>
+      <c r="K14" s="15">
+        <f>IF(H14&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 101: Kristiansand Folkebibliotek</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Kultur og innbyggerdialog</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>35000000.01</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>35000000.01</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>34200000.01</v>
+      </c>
+      <c r="G15" s="12">
+        <f>E15-F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="13">
+        <f>IF(F15&gt;0, E15/F15, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>IF(H15&gt;0, D15/H15, D15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="12">
+        <f>I15-D15</f>
+        <v/>
+      </c>
+      <c r="K15" s="15">
+        <f>IF(H15&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 202: Lovisenlev Skole</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>39449999.99</v>
+      </c>
+      <c r="G16" s="12">
+        <f>E16-F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="13">
+        <f>IF(F16&gt;0, E16/F16, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="14">
+        <f>IF(H16&gt;0, D16/H16, D16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="12">
+        <f>I16-D16</f>
+        <v/>
+      </c>
+      <c r="K16" s="15">
+        <f>IF(H16&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 203: Vågsbygd Skole</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>41999999.99</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>41999999.99</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>43650000</v>
+      </c>
+      <c r="G17" s="12">
+        <f>E17-F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="13">
+        <f>IF(F17&gt;0, E17/F17, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="14">
+        <f>IF(H17&gt;0, D17/H17, D17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="12">
+        <f>I17-D17</f>
+        <v/>
+      </c>
+      <c r="K17" s="15">
+        <f>IF(H17&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 204: Grim Ungdomsskole</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>44999999.99</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>44999999.99</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>46200000</v>
+      </c>
+      <c r="G18" s="12">
+        <f>E18-F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="13">
+        <f>IF(F18&gt;0, E18/F18, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I18" s="14">
+        <f>IF(H18&gt;0, D18/H18, D18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="12">
+        <f>I18-D18</f>
+        <v/>
+      </c>
+      <c r="K18" s="15">
+        <f>IF(H18&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 211: Lund Kommunale Barnehage</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>27999999.99</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>27999999.99</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>29149999.99</v>
+      </c>
+      <c r="G19" s="12">
+        <f>E19-F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="13">
+        <f>IF(F19&gt;0, E19/F19, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I19" s="14">
+        <f>IF(H19&gt;0, D19/H19, D19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="12">
+        <f>I19-D19</f>
+        <v/>
+      </c>
+      <c r="K19" s="15">
+        <f>IF(H19&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 301: Byggesak og Tilsyn</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>By- og stedsutvikling</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>41999999.99</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>41999999.99</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>45300000</v>
+      </c>
+      <c r="G20" s="12">
+        <f>E20-F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="13">
+        <f>IF(F20&gt;0, E20/F20, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I20" s="14">
+        <f>IF(H20&gt;0, D20/H20, D20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="12">
+        <f>I20-D20</f>
+        <v/>
+      </c>
+      <c r="K20" s="15">
+        <f>IF(H20&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 302: Vann, Avløp og Renovasjon</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>By- og stedsutvikling</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>319999999.99</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>319999999.99</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>319999999.99</v>
+      </c>
+      <c r="G21" s="12">
+        <f>E21-F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="13">
+        <f>IF(F21&gt;0, E21/F21, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>IF(H21&gt;0, D21/H21, D21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="12">
+        <f>I21-D21</f>
+        <v/>
+      </c>
+      <c r="K21" s="15">
+        <f>IF(H21&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 401: Strai Sykehjem &amp; Omsorgsboliger</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>61999999.99</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>61999999.99</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>64350000</v>
+      </c>
+      <c r="G22" s="12">
+        <f>E22-F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="13">
+        <f>IF(F22&gt;0, E22/F22, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I22" s="14">
+        <f>IF(H22&gt;0, D22/H22, D22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>I22-D22</f>
+        <v/>
+      </c>
+      <c r="K22" s="15">
+        <f>IF(H22&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 402: Hjemmetjenesten Vågsbygd</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>56799999.99</v>
+      </c>
+      <c r="G23" s="12">
+        <f>E23-F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="13">
+        <f>IF(F23&gt;0, E23/F23, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>IF(H23&gt;0, D23/H23, D23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="12">
+        <f>I23-D23</f>
+        <v/>
+      </c>
+      <c r="K23" s="15">
+        <f>IF(H23&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 403: Sørlandsparken Bo- og Miljøtjeneste</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>47999999.99</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>47999999.99</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="G24" s="12">
+        <f>E24-F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="13">
+        <f>IF(F24&gt;0, E24/F24, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="14">
+        <f>IF(H24&gt;0, D24/H24, D24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="12">
+        <f>I24-D24</f>
+        <v/>
+      </c>
+      <c r="K24" s="15">
+        <f>IF(H24&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 404: Presteheia Omsorgssenter</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>70099999.98999999</v>
+      </c>
+      <c r="G25" s="12">
+        <f>E25-F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="13">
+        <f>IF(F25&gt;0, E25/F25, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>IF(H25&gt;0, D25/H25, D25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>I25-D25</f>
+        <v/>
+      </c>
+      <c r="K25" s="15">
+        <f>IF(H25&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 501: IKT Drift &amp; Brukerstøtte</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Organisasjon og teknologi</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>179999999.99</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>179999999.99</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>180200000</v>
+      </c>
+      <c r="G26" s="12">
+        <f>E26-F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="13">
+        <f>IF(F26&gt;0, E26/F26, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="14">
+        <f>IF(H26&gt;0, D26/H26, D26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="12">
+        <f>I26-D26</f>
+        <v/>
+      </c>
+      <c r="K26" s="15">
+        <f>IF(H26&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Enhet 601: Finans- og Likviditetsforvaltning</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Økonomi og virksomhetsstyring</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>420000000.01</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>420000000.01</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>412500000</v>
+      </c>
+      <c r="G27" s="12">
+        <f>E27-F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="13">
+        <f>IF(F27&gt;0, E27/F27, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>IF(H27&gt;0, D27/H27, D27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="12">
+        <f>I27-D27</f>
+        <v/>
+      </c>
+      <c r="K27" s="15">
+        <f>IF(H27&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Grunnskoleavdelingen (28 skoler)</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>920000000</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>920000000</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>936800000.01</v>
+      </c>
+      <c r="G28" s="12">
+        <f>E28-F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="13">
+        <f>IF(F28&gt;0, E28/F28, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>IF(H28&gt;0, D28/H28, D28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="12">
+        <f>I28-D28</f>
+        <v/>
+      </c>
+      <c r="K28" s="15">
+        <f>IF(H28&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Hjemmetjenester og rehabilitering</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>820000000</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>820000000</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>831199999.99</v>
+      </c>
+      <c r="G29" s="12">
+        <f>E29-F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="13">
+        <f>IF(F29&gt;0, E29/F29, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>IF(H29&gt;0, D29/H29, D29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="12">
+        <f>I29-D29</f>
+        <v/>
+      </c>
+      <c r="K29" s="15">
+        <f>IF(H29&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>IKT Drift — Cloud &amp; FinOps</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Organisasjon og teknologi</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>44999999.99</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>44999999.99</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>44200000</v>
+      </c>
+      <c r="G30" s="12">
+        <f>E30-F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="13">
+        <f>IF(F30&gt;0, E30/F30, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I30" s="14">
+        <f>IF(H30&gt;0, D30/H30, D30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="12">
+        <f>I30-D30</f>
+        <v/>
+      </c>
+      <c r="K30" s="15">
+        <f>IF(H30&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Ingeniørvesenet (Vann, Avløp &amp; Renovasjon)</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>By- og stedsutvikling</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="G31" s="12">
+        <f>E31-F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="13">
+        <f>IF(F31&gt;0, E31/F31, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I31" s="14">
+        <f>IF(H31&gt;0, D31/H31, D31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="12">
+        <f>I31-D31</f>
+        <v/>
+      </c>
+      <c r="K31" s="15">
+        <f>IF(H31&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Kommunal Boenhet</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>50339572</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>39650784</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>47426243.51</v>
+      </c>
+      <c r="G32" s="12">
+        <f>E32-F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="13">
+        <f>IF(F32&gt;0, E32/F32, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I32" s="14">
+        <f>IF(H32&gt;0, D32/H32, D32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="12">
+        <f>I32-D32</f>
+        <v/>
+      </c>
+      <c r="K32" s="15">
+        <f>IF(H32&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Kommunal Boenhet (Enhet 2540)</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>14500000.01</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>14500000.01</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>15649999.99</v>
+      </c>
+      <c r="G33" s="12">
+        <f>E33-F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="13">
+        <f>IF(F33&gt;0, E33/F33, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I33" s="14">
+        <f>IF(H33&gt;0, D33/H33, D33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="12">
+        <f>I33-D33</f>
+        <v/>
+      </c>
+      <c r="K33" s="15">
+        <f>IF(H33&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Kommunal Skole</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>33591000</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>31983000</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>36080000</v>
+      </c>
+      <c r="G34" s="12">
+        <f>E34-F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="13">
+        <f>IF(F34&gt;0, E34/F34, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I34" s="14">
+        <f>IF(H34&gt;0, D34/H34, D34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="12">
+        <f>I34-D34</f>
+        <v/>
+      </c>
+      <c r="K34" s="15">
+        <f>IF(H34&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Kommunalsjefens fagstab Helse</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>24499999.99</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>24499999.99</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>25299999.99</v>
+      </c>
+      <c r="G35" s="12">
+        <f>E35-F35</f>
+        <v/>
+      </c>
+      <c r="H35" s="13">
+        <f>IF(F35&gt;0, E35/F35, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I35" s="14">
+        <f>IF(H35&gt;0, D35/H35, D35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="12">
+        <f>I35-D35</f>
+        <v/>
+      </c>
+      <c r="K35" s="15">
+        <f>IF(H35&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Kommunalsjefens fagstab Oppvekst</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>21999999.99</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>21999999.99</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="G36" s="12">
+        <f>E36-F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="13">
+        <f>IF(F36&gt;0, E36/F36, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I36" s="14">
+        <f>IF(H36&gt;0, D36/H36, D36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="12">
+        <f>I36-D36</f>
+        <v/>
+      </c>
+      <c r="K36" s="15">
+        <f>IF(H36&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Kommunalsjefens stab Byutvikling</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>By- og stedsutvikling</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>179999999.99</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>179999999.99</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>181500000.01</v>
+      </c>
+      <c r="G37" s="12">
+        <f>E37-F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="13">
+        <f>IF(F37&gt;0, E37/F37, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I37" s="14">
+        <f>IF(H37&gt;0, D37/H37, D37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="12">
+        <f>I37-D37</f>
+        <v/>
+      </c>
+      <c r="K37" s="15">
+        <f>IF(H37&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Kommunalsjefens stab Kultur</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Kultur og innbyggerdialog</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>239400000</v>
+      </c>
+      <c r="G38" s="12">
+        <f>E38-F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="13">
+        <f>IF(F38&gt;0, E38/F38, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I38" s="14">
+        <f>IF(H38&gt;0, D38/H38, D38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="12">
+        <f>I38-D38</f>
+        <v/>
+      </c>
+      <c r="K38" s="15">
+        <f>IF(H38&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Kommunalsjefens stab Org &amp; Tek</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Organisasjon og teknologi</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>60000000.01</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>60000000.01</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>60000000.01</v>
+      </c>
+      <c r="G39" s="12">
+        <f>E39-F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="13">
+        <f>IF(F39&gt;0, E39/F39, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I39" s="14">
+        <f>IF(H39&gt;0, D39/H39, D39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="12">
+        <f>I39-D39</f>
+        <v/>
+      </c>
+      <c r="K39" s="15">
+        <f>IF(H39&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Kommunedirektørens stab</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Konsernledelsen / Bystyret</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>80000000.01000001</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>80000000.01000001</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>80000000.01000001</v>
+      </c>
+      <c r="G40" s="12">
+        <f>E40-F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="13">
+        <f>IF(F40&gt;0, E40/F40, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I40" s="14">
+        <f>IF(H40&gt;0, D40/H40, D40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="12">
+        <f>I40-D40</f>
+        <v/>
+      </c>
+      <c r="K40" s="15">
+        <f>IF(H40&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Konsernregnskap og Lønnssentral</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Økonomi og virksomhetsstyring</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>64999999.99</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>64999999.99</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>64999999.99</v>
+      </c>
+      <c r="G41" s="12">
+        <f>E41-F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="13">
+        <f>IF(F41&gt;0, E41/F41, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I41" s="14">
+        <f>IF(H41&gt;0, D41/H41, D41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="12">
+        <f>I41-D41</f>
+        <v/>
+      </c>
+      <c r="K41" s="15">
+        <f>IF(H41&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Lovisenlev Skole — Skolefritidsordning</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>6000000.01</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>6000000.01</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>6350000</v>
+      </c>
+      <c r="G42" s="12">
+        <f>E42-F42</f>
+        <v/>
+      </c>
+      <c r="H42" s="13">
+        <f>IF(F42&gt;0, E42/F42, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I42" s="14">
+        <f>IF(H42&gt;0, D42/H42, D42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="12">
+        <f>I42-D42</f>
+        <v/>
+      </c>
+      <c r="K42" s="15">
+        <f>IF(H42&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Lovisenlev Skole — Småtrinnet</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>13999999.99</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>13999999.99</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>14399999.99</v>
+      </c>
+      <c r="G43" s="12">
+        <f>E43-F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="13">
+        <f>IF(F43&gt;0, E43/F43, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I43" s="14">
+        <f>IF(H43&gt;0, D43/H43, D43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="12">
+        <f>I43-D43</f>
+        <v/>
+      </c>
+      <c r="K43" s="15">
+        <f>IF(H43&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Plan- og bygningsetaten</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>By- og stedsutvikling</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>66700000</v>
+      </c>
+      <c r="G44" s="12">
+        <f>E44-F44</f>
+        <v/>
+      </c>
+      <c r="H44" s="13">
+        <f>IF(F44&gt;0, E44/F44, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I44" s="14">
+        <f>IF(H44&gt;0, D44/H44, D44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="12">
+        <f>I44-D44</f>
+        <v/>
+      </c>
+      <c r="K44" s="15">
+        <f>IF(H44&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Sentral økonomistab</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Økonomi og virksomhetsstyring</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>49999999.99</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>49999999.99</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>49999999.99</v>
+      </c>
+      <c r="G45" s="12">
+        <f>E45-F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="13">
+        <f>IF(F45&gt;0, E45/F45, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I45" s="14">
+        <f>IF(H45&gt;0, D45/H45, D45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="12">
+        <f>I45-D45</f>
+        <v/>
+      </c>
+      <c r="K45" s="15">
+        <f>IF(H45&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Sentraladministrasjonen</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Fellestjenester</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="G46" s="12">
+        <f>E46-F46</f>
+        <v/>
+      </c>
+      <c r="H46" s="13">
+        <f>IF(F46&gt;0, E46/F46, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I46" s="14">
+        <f>IF(H46&gt;0, D46/H46, D46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="12">
+        <f>I46-D46</f>
+        <v/>
+      </c>
+      <c r="K46" s="15">
+        <f>IF(H46&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Sentrale Økonomitjenester / Hub Koordinator</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Konsern, Helse &amp; Oppvekst</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="G47" s="12">
+        <f>E47-F47</f>
+        <v/>
+      </c>
+      <c r="H47" s="13">
+        <f>IF(F47&gt;0, E47/F47, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I47" s="14">
+        <f>IF(H47&gt;0, D47/H47, D47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="12">
+        <f>I47-D47</f>
+        <v/>
+      </c>
+      <c r="K47" s="15">
+        <f>IF(H47&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Strai Sykehjem — Avd. Demens</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>18000000.01</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>18000000.01</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>18800000.01</v>
+      </c>
+      <c r="G48" s="12">
+        <f>E48-F48</f>
+        <v/>
+      </c>
+      <c r="H48" s="13">
+        <f>IF(F48&gt;0, E48/F48, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I48" s="14">
+        <f>IF(H48&gt;0, D48/H48, D48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="12">
+        <f>I48-D48</f>
+        <v/>
+      </c>
+      <c r="K48" s="15">
+        <f>IF(H48&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Strai Sykehjem — Somatisk Korttidsavd.</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>15999999.99</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>15999999.99</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>16650000.01</v>
+      </c>
+      <c r="G49" s="12">
+        <f>E49-F49</f>
+        <v/>
+      </c>
+      <c r="H49" s="13">
+        <f>IF(F49&gt;0, E49/F49, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I49" s="14">
+        <f>IF(H49&gt;0, D49/H49, D49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="12">
+        <f>I49-D49</f>
+        <v/>
+      </c>
+      <c r="K49" s="15">
+        <f>IF(H49&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>VAR Ingeniørvesenet — Renseanlegg Lund</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>By- og stedsutvikling</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="G50" s="12">
+        <f>E50-F50</f>
+        <v/>
+      </c>
+      <c r="H50" s="13">
+        <f>IF(F50&gt;0, E50/F50, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I50" s="14">
+        <f>IF(H50&gt;0, D50/H50, D50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="12">
+        <f>I50-D50</f>
+        <v/>
+      </c>
+      <c r="K50" s="15">
+        <f>IF(H50&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Økonomitjenesten Byutvikling</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>By- og stedsutvikling</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="G51" s="12">
+        <f>E51-F51</f>
+        <v/>
+      </c>
+      <c r="H51" s="13">
+        <f>IF(F51&gt;0, E51/F51, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I51" s="14">
+        <f>IF(H51&gt;0, D51/H51, D51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="12">
+        <f>I51-D51</f>
+        <v/>
+      </c>
+      <c r="K51" s="15">
+        <f>IF(H51&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Økonomitjenesten Helse</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Helse og mestring</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>13999999.99</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>13999999.99</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>14500000.01</v>
+      </c>
+      <c r="G52" s="12">
+        <f>E52-F52</f>
+        <v/>
+      </c>
+      <c r="H52" s="13">
+        <f>IF(F52&gt;0, E52/F52, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I52" s="14">
+        <f>IF(H52&gt;0, D52/H52, D52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="12">
+        <f>I52-D52</f>
+        <v/>
+      </c>
+      <c r="K52" s="15">
+        <f>IF(H52&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Økonomitjenesten Kultur &amp; Felles</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Kultur, Dialog, Org &amp; Teknologi</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>9999999.99</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>9999999.99</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>9999999.99</v>
+      </c>
+      <c r="G53" s="12">
+        <f>E53-F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="13">
+        <f>IF(F53&gt;0, E53/F53, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I53" s="14">
+        <f>IF(H53&gt;0, D53/H53, D53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="12">
+        <f>I53-D53</f>
+        <v/>
+      </c>
+      <c r="K53" s="15">
+        <f>IF(H53&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Økonomitjenesten Oppvekst</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Oppvekst og utdanning</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="G54" s="12">
+        <f>E54-F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="13">
+        <f>IF(F54&gt;0, E54/F54, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I54" s="14">
+        <f>IF(H54&gt;0, D54/H54, D54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="12">
+        <f>I54-D54</f>
+        <v/>
+      </c>
+      <c r="K54" s="15">
+        <f>IF(H54&lt;0.9, "🚨 Merforbruk &gt; 10% — Krever tiltak", "🟢 I rute")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>TOTALT</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>Kristiansand Kommune</t>
         </is>
       </c>
-      <c r="D14" s="17">
-        <f>SUM(D12:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="17">
-        <f>SUM(E12:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="17">
-        <f>SUM(F12:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="17">
-        <f>SUM(G12:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18">
-        <f>IF(F14&gt;0, E14/F14, 1.0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(H14&gt;0, D14/H14, D14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="17">
-        <f>I14-D14</f>
-        <v/>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="D55" s="17">
+        <f>SUM(D12:D54)</f>
+        <v/>
+      </c>
+      <c r="E55" s="17">
+        <f>SUM(E12:E54)</f>
+        <v/>
+      </c>
+      <c r="F55" s="17">
+        <f>SUM(F12:F54)</f>
+        <v/>
+      </c>
+      <c r="G55" s="17">
+        <f>SUM(G12:G54)</f>
+        <v/>
+      </c>
+      <c r="H55" s="18">
+        <f>IF(F55&gt;0, E55/F55, 1.0)</f>
+        <v/>
+      </c>
+      <c r="I55" s="17">
+        <f>IF(H55&gt;0, D55/H55, D55)</f>
+        <v/>
+      </c>
+      <c r="J55" s="17">
+        <f>I55-D55</f>
+        <v/>
+      </c>
+      <c r="K55" s="16" t="inlineStr">
         <is>
           <t>Konsernvurdering</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>ℹ️ VURDERING FRA CONTROLLER (Jf. Kommuneloven § 14-5 &amp; Handlings- og økonomiplan):</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="19" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>• Merforbruket i Skole (-4,1 MNOK) skyldes primært overtid og vikarforbruk utløst av høyt sykefravær ved skolestart.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="19" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>• Merforbruket i Bo- og miljøtjenesten (-7,8 MNOK) er knyttet til forsinkede refusjoner for ressurskrevende tjenester fra staten samt innleie.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="19" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>• Netto driftsresultat holdes under kontroll via overføring fra sentralt disposisjonsfond ved Formannskapets T2-behandling i september 2026.</t>
         </is>
@@ -966,9 +2647,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -1043,24 +2724,24 @@
     <row r="6">
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Døgnomsorg og Sykehjem</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_FASTLØNNLÆRE</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Fast lønn lærere</t>
+          <t>Ekstern rådgivning, juss og konsulenter</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>15729000</v>
+        <v>143999999.99</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>18197000</v>
+        <v>162249999.99</v>
       </c>
       <c r="G6" s="12">
         <f>E6-F6</f>
@@ -1083,24 +2764,24 @@
     <row r="7">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Grunnskoleavdelingen (28 skoler)</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_LØNNTILVIKAR</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Lønn til vikarer</t>
+          <t>Sykemeldte vikarer og kortere vikariat</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>202000</v>
+        <v>138000000</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>847000</v>
+        <v>154800000.01</v>
       </c>
       <c r="G7" s="12">
         <f>E7-F7</f>
@@ -1123,24 +2804,24 @@
     <row r="8">
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Hjemmetjenester og rehabilitering</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_ARBEIDSGIVER</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Arbeidsgiveravgift</t>
+          <t>Overtid og ubekvem arbeidstid</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>3785000</v>
+        <v>123000000</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>4216000</v>
+        <v>134199999.99</v>
       </c>
       <c r="G8" s="12">
         <f>E8-F8</f>
@@ -1163,24 +2844,24 @@
     <row r="9">
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Boenhet</t>
+          <t>Barnehageavdelingen (54 barnehager)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Kjøp fra private og næringsliv</t>
+          <t>Sykemeldte vikarer og kortere vikariat</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0</v>
+        <v>108000000.01</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>382656</v>
+        <v>119000000</v>
       </c>
       <c r="G9" s="12">
         <f>E9-F9</f>
@@ -1203,24 +2884,24 @@
     <row r="10">
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Enhet 301: Byggesak og Tilsyn</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_OVERTIDSLØNN</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Overtidslønn</t>
+          <t>Foreldrebetaling SFO og barnehage</t>
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>57000</v>
+        <v>6299999.99</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>436000</v>
+        <v>9600000</v>
       </c>
       <c r="G10" s="12">
         <f>E10-F10</f>
@@ -1243,24 +2924,24 @@
     <row r="11">
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Boenhet</t>
+          <t>Kommunal Skole</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>SKOLE_FASTLØNNLÆRE</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Refusjon sykepenger</t>
+          <t>Fast lønn lærere</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>-1791385</v>
+        <v>15729000</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>-1465410</v>
+        <v>18197000</v>
       </c>
       <c r="G11" s="12">
         <f>E11-F11</f>
@@ -1283,24 +2964,24 @@
     <row r="12">
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Boenhet</t>
+          <t>Enhet 403: Sørlandsparken Bo- og Miljøtjeneste</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Utrykning, klesgodtgjørelse o.l.</t>
+          <t>Ekstern rådgivning, juss og konsulenter</t>
         </is>
       </c>
       <c r="E12" s="11" t="n">
-        <v>66474</v>
+        <v>7199999.99</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>375138.84</v>
+        <v>9600000</v>
       </c>
       <c r="G12" s="12">
         <f>E12-F12</f>
@@ -1323,24 +3004,24 @@
     <row r="13">
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Boenhet</t>
+          <t>Enhet 401: Strai Sykehjem &amp; Omsorgsboliger</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Sykemeldte vikarer og kortere vikariat</t>
+          <t>Overtid og ubekvem arbeidstid</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7069784</v>
+        <v>9299999.99</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7349401.74</v>
+        <v>11650000</v>
       </c>
       <c r="G13" s="12">
         <f>E13-F13</f>
@@ -1363,24 +3044,24 @@
     <row r="14">
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Enhet 404: Presteheia Omsorgssenter</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_SYKEVIKARER</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Sykevikarer</t>
+          <t>Overtid og ubekvem arbeidstid</t>
         </is>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0</v>
+        <v>10200000</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>272000</v>
+        <v>12299999.99</v>
       </c>
       <c r="G14" s="12">
         <f>E14-F14</f>
@@ -1403,24 +3084,24 @@
     <row r="15">
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Enhet 402: Hjemmetjenesten Vågsbygd</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_MERVERDIAVGI</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Merverdiavgift som gir rett til merverdiavgiftskompensa…</t>
+          <t>Sykemeldte vikarer og kortere vikariat</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0</v>
+        <v>8250000</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>262000</v>
+        <v>10049999.99</v>
       </c>
       <c r="G15" s="12">
         <f>E15-F15</f>
@@ -1443,24 +3124,24 @@
     <row r="16">
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Enhet 203: Vågsbygd Skole</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_AVSETNINGERT</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Avsetninger til bundne fond - 1B</t>
+          <t>Sykemeldte vikarer og kortere vikariat</t>
         </is>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0</v>
+        <v>6299999.99</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>250000</v>
+        <v>7950000</v>
       </c>
       <c r="G16" s="12">
         <f>E16-F16</f>
@@ -1483,24 +3164,24 @@
     <row r="17">
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Boenhet</t>
+          <t>Kommunalsjefens stab Byutvikling</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Timelønnede ekstrahjelper</t>
+          <t>Kjøp fra private og næringsliv</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0</v>
+        <v>26999999.99</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>209539.66</v>
+        <v>28500000.01</v>
       </c>
       <c r="G17" s="12">
         <f>E17-F17</f>
@@ -1523,24 +3204,24 @@
     <row r="18">
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Enhet 202: Lovisenlev Skole</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_PENSJONSPK</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Pensjon SPK</t>
+          <t>Sykemeldte vikarer og kortere vikariat</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>1910000</v>
+        <v>5700000</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2098000</v>
+        <v>7149999.99</v>
       </c>
       <c r="G18" s="12">
         <f>E18-F18</f>
@@ -1563,24 +3244,24 @@
     <row r="19">
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Enhet 204: Grim Ungdomsskole</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_PENSJONSINNS</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Pensjonsinnskudd og trekkpliktige forsikringsordninger</t>
+          <t>Sykemeldte vikarer og kortere vikariat</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1559000</v>
+        <v>6749999.99</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1734000</v>
+        <v>7950000</v>
       </c>
       <c r="G19" s="12">
         <f>E19-F19</f>
@@ -1603,24 +3284,24 @@
     <row r="20">
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Boenhet</t>
+          <t>Enhet 211: Lund Kommunale Barnehage</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Lærlingelønn</t>
+          <t>Sykemeldte vikarer og kortere vikariat</t>
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>85000</v>
+        <v>4199999.99</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>242075.85</v>
+        <v>5349999.99</v>
       </c>
       <c r="G20" s="12">
         <f>E20-F20</f>
@@ -1643,24 +3324,24 @@
     <row r="21">
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Kommunal Boenhet (Enhet 2540)</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_BRUKAVBUNDNE</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Bruk av bundne driftsfond - 1B</t>
+          <t>Overtid og ubekvem arbeidstid</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-142000</v>
+        <v>2175000.01</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0</v>
+        <v>3324999.99</v>
       </c>
       <c r="G21" s="12">
         <f>E21-F21</f>
@@ -1683,24 +3364,24 @@
     <row r="22">
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Kommunalsjefens fagstab Helse</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_LØNNTILEKSTR</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Lønn til ekstrahjelp</t>
+          <t>Kursavgifter og etterutdanning</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>80000</v>
+        <v>3674999.99</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>205000</v>
+        <v>4474999.99</v>
       </c>
       <c r="G22" s="12">
         <f>E22-F22</f>
@@ -1723,24 +3404,24 @@
     <row r="23">
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Boenhet</t>
+          <t>Strai Sykehjem — Avd. Demens</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Kompensasjon for merverdiavgift</t>
+          <t>Overtid og ubekvem arbeidstid</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>-140000</v>
+        <v>2700000.01</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>-35217.28</v>
+        <v>3500000.01</v>
       </c>
       <c r="G23" s="12">
         <f>E23-F23</f>
@@ -1763,24 +3444,24 @@
     <row r="24">
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Strai Sykehjem — Somatisk Korttidsavd.</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_IKTUTSTYROGT</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>IKT-utstyr og telefon</t>
+          <t>Driftsrekvisita, verneutstyr og kjemikalier</t>
         </is>
       </c>
       <c r="E24" s="11" t="n">
-        <v>284000</v>
+        <v>2399999.99</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>386000</v>
+        <v>3050000.01</v>
       </c>
       <c r="G24" s="12">
         <f>E24-F24</f>
@@ -1808,19 +3489,19 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_SERVICEAVTAL</t>
+          <t>SKOLE_LØNNTILVIKAR</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Serviceavtaler, reparasjoner og vaktmestertjenester</t>
+          <t>Lønn til vikarer</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>20000</v>
+        <v>202000</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>96000</v>
+        <v>847000</v>
       </c>
       <c r="G25" s="12">
         <f>E25-F25</f>
@@ -1843,24 +3524,24 @@
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Økonomitjenesten Helse</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_AVGIFTERGEBY</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Avgifter, gebyrer, lisenser o.l.</t>
+          <t>Ekstern rådgivning, juss og konsulenter</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0</v>
+        <v>2099999.99</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>60000</v>
+        <v>2600000.01</v>
       </c>
       <c r="G26" s="12">
         <f>E26-F26</f>
@@ -1883,24 +3564,24 @@
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Kommunalsjefens fagstab Oppvekst</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_KJØPFRAINTER</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Kjøp fra interkommunale selskap/private</t>
+          <t>Kursavgifter og etterutdanning</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0</v>
+        <v>3299999.99</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>48000</v>
+        <v>3800000</v>
       </c>
       <c r="G27" s="12">
         <f>E27-F27</f>
@@ -1923,24 +3604,24 @@
     <row r="28">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Økonomitjenesten Oppvekst</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_LÆREBØKER</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Lærebøker</t>
+          <t>Ekstern rådgivning, juss og konsulenter</t>
         </is>
       </c>
       <c r="E28" s="11" t="n">
-        <v>110000</v>
+        <v>2250000</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>158000</v>
+        <v>2750000</v>
       </c>
       <c r="G28" s="12">
         <f>E28-F28</f>
@@ -1968,19 +3649,19 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_KJØPFRAANDRE</t>
+          <t>SKOLE_ARBEIDSGIVER</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Kjøp fra andre (private)</t>
+          <t>Arbeidsgiveravgift</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>207000</v>
+        <v>3785000</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>243000</v>
+        <v>4216000</v>
       </c>
       <c r="G29" s="12">
         <f>E29-F29</f>
@@ -2003,24 +3684,24 @@
     <row r="30">
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Kommunal Skole</t>
+          <t>Lovisenlev Skole — Småtrinnet</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>SKOLE_REFUSJONFRAK</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Refusjon fra kommuner</t>
+          <t>Lærebøker og digitale læremidler</t>
         </is>
       </c>
       <c r="E30" s="11" t="n">
-        <v>-35000</v>
+        <v>2099999.99</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0</v>
+        <v>2499999.99</v>
       </c>
       <c r="G30" s="12">
         <f>E30-F30</f>
